--- a/research/traditional_assets/database/data/brazil/brazil_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/brazil/brazil_brokerage_investment_banking.xlsx
@@ -588,124 +588,112 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.38</v>
+        <v>0.433</v>
       </c>
       <c r="E2">
-        <v>0.375</v>
+        <v>0.283</v>
       </c>
       <c r="F2">
-        <v>0.363</v>
+        <v>0.3695</v>
       </c>
       <c r="G2">
-        <v>0.2306633004360799</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>0.2306633004360799</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>0.2906587101216433</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>0.2505802749738104</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>606.5999999999999</v>
+        <v>712.8</v>
       </c>
       <c r="L2">
-        <v>0.2784484737204498</v>
+        <v>0.2764612341465307</v>
       </c>
       <c r="M2">
-        <v>20.43</v>
+        <v>325.04</v>
       </c>
       <c r="N2">
-        <v>0.001234627587248829</v>
+        <v>0.03665437486608702</v>
       </c>
       <c r="O2">
-        <v>0.03367952522255193</v>
+        <v>0.4560044893378227</v>
       </c>
       <c r="P2">
-        <v>3.13</v>
+        <v>13.8</v>
       </c>
       <c r="Q2">
-        <v>0.0001891524399456111</v>
+        <v>0.001556209614668967</v>
       </c>
       <c r="R2">
-        <v>0.005159907682162876</v>
+        <v>0.01936026936026936</v>
       </c>
       <c r="S2">
-        <v>17.3</v>
+        <v>311.24</v>
       </c>
       <c r="T2">
-        <v>0.846793930494371</v>
+        <v>0.9575436869308395</v>
       </c>
       <c r="U2">
-        <v>811.7</v>
+        <v>793.1</v>
       </c>
       <c r="V2">
-        <v>0.04905272699803596</v>
+        <v>0.08943694531840274</v>
       </c>
       <c r="W2">
-        <v>0.312912609527052</v>
+        <v>0.1687851314485103</v>
       </c>
       <c r="X2">
-        <v>0.05348594310598127</v>
+        <v>0.1357186328220107</v>
       </c>
       <c r="Y2">
-        <v>0.2594266664210708</v>
+        <v>0.0330664986264996</v>
       </c>
       <c r="Z2">
-        <v>0.2675885584856342</v>
+        <v>0.2356678000804358</v>
       </c>
       <c r="AA2">
-        <v>0.03751723821378494</v>
+        <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04929594526092099</v>
+        <v>0.09211582451234428</v>
       </c>
       <c r="AC2">
-        <v>-0.01177870704713604</v>
+        <v>-0.09211582451234428</v>
       </c>
       <c r="AD2">
-        <v>5580.599999999999</v>
+        <v>14401</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>5580.599999999999</v>
+        <v>14401</v>
       </c>
       <c r="AG2">
-        <v>4768.9</v>
+        <v>13607.9</v>
       </c>
       <c r="AH2">
-        <v>0.2521951726537751</v>
+        <v>0.6189000674726134</v>
       </c>
       <c r="AI2">
-        <v>0.6723209445214143</v>
+        <v>0.8058036213881242</v>
       </c>
       <c r="AJ2">
-        <v>0.2237197650635191</v>
+        <v>0.6054521347594726</v>
       </c>
       <c r="AK2">
-        <v>0.63680429441299</v>
+        <v>0.796785431975876</v>
       </c>
       <c r="AL2">
-        <v>15.7</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>14.68</v>
-      </c>
-      <c r="AN2">
-        <v>8.513501144164758</v>
-      </c>
-      <c r="AO2">
-        <v>40.33121019108281</v>
-      </c>
-      <c r="AP2">
-        <v>7.275209763539283</v>
-      </c>
-      <c r="AQ2">
-        <v>43.13351498637603</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>XP Inc. (NasdaqGS:XP)</t>
+          <t>Banco Modal S.A. (BOVESPA:MODL3)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,116 +712,113 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.433</v>
+      </c>
+      <c r="E3">
+        <v>0.283</v>
+      </c>
       <c r="F3">
-        <v>0.363</v>
+        <v>0.578</v>
       </c>
       <c r="G3">
-        <v>0.2430118967018087</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>0.2430118967018087</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.306219170132508</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>0.2922236880350436</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>590.3</v>
+        <v>13.4</v>
       </c>
       <c r="L3">
-        <v>0.2854724828319953</v>
+        <v>0.08695652173913045</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>21.34</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.07384083044982699</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>1.592537313432836</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>13.8</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.04775086505190312</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>1.029850746268657</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>7.539999999999999</v>
+      </c>
+      <c r="T3">
+        <v>0.3533270852858481</v>
       </c>
       <c r="U3">
-        <v>520.5</v>
+        <v>312.5</v>
       </c>
       <c r="V3">
-        <v>0.03236658499881851</v>
+        <v>1.081314878892734</v>
       </c>
       <c r="W3">
-        <v>0.3825416369645518</v>
+        <v>0.0551213492389963</v>
       </c>
       <c r="X3">
-        <v>0.05382012901293953</v>
+        <v>0.1270468748878684</v>
       </c>
       <c r="Y3">
-        <v>0.3287215079516123</v>
+        <v>-0.07192552564887211</v>
       </c>
       <c r="Z3">
-        <v>0.256770684581093</v>
+        <v>1.975641025641026</v>
       </c>
       <c r="AA3">
-        <v>0.07503447642756989</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.04914689037764965</v>
+        <v>0.09190485303815316</v>
       </c>
       <c r="AC3">
-        <v>0.02588758604992024</v>
+        <v>-0.09190485303815316</v>
       </c>
       <c r="AD3">
-        <v>5437.9</v>
+        <v>324.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>5437.9</v>
+        <v>324.4</v>
       </c>
       <c r="AG3">
-        <v>4917.4</v>
+        <v>11.89999999999998</v>
       </c>
       <c r="AH3">
-        <v>0.2526987402006571</v>
+        <v>0.5288555591783501</v>
       </c>
       <c r="AI3">
-        <v>0.6870633125702806</v>
+        <v>0.5715292459478507</v>
       </c>
       <c r="AJ3">
-        <v>0.2341752862068309</v>
+        <v>0.03954802259886998</v>
       </c>
       <c r="AK3">
-        <v>0.6650347569716805</v>
+        <v>0.04664837318698541</v>
       </c>
       <c r="AL3">
-        <v>15.7</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>14.68</v>
-      </c>
-      <c r="AN3">
-        <v>8.295804729214339</v>
-      </c>
-      <c r="AO3">
-        <v>40.33121019108281</v>
-      </c>
-      <c r="AP3">
-        <v>7.501754385964912</v>
-      </c>
-      <c r="AQ3">
-        <v>43.13351498637603</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -844,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Banco Modal S.A. (BOVESPA:MODL3)</t>
+          <t>XP Inc. (NasdaqGS:XP)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -852,11 +837,8 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.38</v>
-      </c>
-      <c r="E4">
-        <v>0.375</v>
+      <c r="F4">
+        <v>0.161</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -871,85 +853,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>16.3</v>
+        <v>699.4</v>
       </c>
       <c r="L4">
-        <v>0.1472448057813912</v>
+        <v>0.2885075488821054</v>
       </c>
       <c r="M4">
-        <v>20.43</v>
+        <v>303.7</v>
       </c>
       <c r="N4">
-        <v>0.04383179575198455</v>
+        <v>0.03540163428025225</v>
       </c>
       <c r="O4">
-        <v>1.253374233128834</v>
+        <v>0.4342293394338004</v>
       </c>
       <c r="P4">
-        <v>3.13</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.006715297146535078</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.1920245398773006</v>
+        <v>-0</v>
       </c>
       <c r="S4">
-        <v>17.3</v>
+        <v>303.7</v>
       </c>
       <c r="T4">
-        <v>0.846793930494371</v>
+        <v>1</v>
       </c>
       <c r="U4">
-        <v>291.2</v>
+        <v>480.6</v>
       </c>
       <c r="V4">
-        <v>0.6247586354859471</v>
+        <v>0.05602247426766293</v>
       </c>
       <c r="W4">
-        <v>0.2432835820895523</v>
+        <v>0.2824489136580244</v>
       </c>
       <c r="X4">
-        <v>0.05315175719902301</v>
+        <v>0.1443903907561531</v>
       </c>
       <c r="Y4">
-        <v>0.1901318248905292</v>
+        <v>0.1380585229018713</v>
       </c>
       <c r="Z4">
-        <v>1.256098944740724</v>
+        <v>0.2231735159817351</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.04944500014419233</v>
+        <v>0.0923267959865354</v>
       </c>
       <c r="AC4">
-        <v>-0.04944500014419233</v>
+        <v>-0.0923267959865354</v>
       </c>
       <c r="AD4">
-        <v>142.7</v>
+        <v>14076.6</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>142.7</v>
+        <v>14076.6</v>
       </c>
       <c r="AG4">
-        <v>-148.5</v>
+        <v>13596</v>
       </c>
       <c r="AH4">
-        <v>0.2343955321944809</v>
+        <v>0.6213380533473403</v>
       </c>
       <c r="AI4">
-        <v>0.3698807672369103</v>
+        <v>0.8134882108183079</v>
       </c>
       <c r="AJ4">
-        <v>-0.4675692695214105</v>
+        <v>0.613131181030634</v>
       </c>
       <c r="AK4">
-        <v>-1.569767441860465</v>
+        <v>0.8081600627697135</v>
       </c>
       <c r="AL4">
         <v>0</v>
